--- a/results_seed_19.xlsx
+++ b/results_seed_19.xlsx
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D1" t="n">
-        <v>0.0312</v>
+        <v>0.0323</v>
       </c>
     </row>
     <row r="2">
